--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,13 +439,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:D145"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="31.54296875" customWidth="1" min="1" max="1"/>
-    <col width="32.54296875" customWidth="1" min="2" max="2"/>
-    <col width="21.453125" customWidth="1" min="3" max="3"/>
-    <col width="77.54296875" customWidth="1" min="4" max="6"/>
+    <col width="31.5703125" customWidth="1" min="1" max="1"/>
+    <col width="32.5703125" customWidth="1" min="2" max="2"/>
+    <col width="29.28515625" customWidth="1" min="3" max="3"/>
+    <col width="77.5703125" customWidth="1" min="4" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2910,6 +2910,198 @@
         </is>
       </c>
     </row>
+    <row r="135" ht="15" customHeight="1">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Le Macchiole</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Messorio</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Kapscandy</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Kapcsandy</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>the Mascot</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TheMascot</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Pingus, Pingus Amelia</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Pingus</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Pingus Amelia is one product category from Pingus</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Branaire Ducru</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Branaire</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="15" customHeight="1">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Chateauneuf du Pape</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CDP</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Gruaud Larose</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Gruaud</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Rousseau chambertin mazis</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Rousseau</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>O'Shaughnessy</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>O'Shaughnessy</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1982 Bordeaux</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BDX82</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>All Bordeaux in vintage 1982</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Beausejour Duffau-Lagarrosse</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Duffau</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -669,12 +669,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Schrader</t>
+          <t>Haut Brion - Blanc</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Schrader</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -682,17 +682,21 @@
           <t>Standalone Producer</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n"/>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Blanc stands for Haut Brion Blanc series</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Schrader</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>HautBailly</t>
+          <t>Schrader</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -705,12 +709,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Mouton</t>
+          <t>HautBailly</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -723,12 +727,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Mouton</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -741,12 +745,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Opus One</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>OpusOne</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -759,12 +763,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Opus One</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>OpusOne</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -777,12 +781,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Colgin</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Colgin</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -795,12 +799,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Rauzan Segla</t>
+          <t>Colgin</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>RauzanSegla</t>
+          <t>Colgin</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -813,12 +817,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Cheval Blanc</t>
+          <t>Rauzan Segla</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>ChevalBlanc</t>
+          <t>RauzanSegla</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -831,12 +835,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Screaming Eagle</t>
+          <t>Cheval Blanc</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>TheFlight</t>
+          <t>ChevalBlanc</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -844,21 +848,17 @@
           <t>Standalone Producer</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>Screaming Eagle The Flight ONLY (excludes flagship Screaming Eagle bottlings)</t>
-        </is>
-      </c>
+      <c r="D21" s="1" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Bond Matriarch</t>
+          <t>Screaming Eagle</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Matriarch</t>
+          <t>TheFlight</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -868,19 +868,19 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Bond Matriarch ONLY (excludes flagship Bond bottlings)</t>
+          <t>Screaming Eagle The Flight ONLY (excludes flagship Screaming Eagle bottlings)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Sassicaia</t>
+          <t>Bond Matriarch</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Stones</t>
+          <t>Matriarch</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -888,17 +888,21 @@
           <t>Standalone Producer</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n"/>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>Bond Matriarch ONLY (excludes flagship Bond bottlings)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Lail</t>
+          <t>Sassicaia</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Lail</t>
+          <t>Stones</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -911,12 +915,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Guigal</t>
+          <t>Lail</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>LALA</t>
+          <t>Lail</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -929,12 +933,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Ausone</t>
+          <t>Guigal</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Ausone</t>
+          <t>LALA</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -947,12 +951,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Dana Estates</t>
+          <t>Ausone</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Lotus</t>
+          <t>Ausone</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -965,12 +969,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Ornellaia</t>
+          <t>Dana Estates</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Ornellaia</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -983,12 +987,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Abreu</t>
+          <t>Ornellaia</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Abreu</t>
+          <t>Ornellaia</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1001,12 +1005,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Dalla Valle</t>
+          <t>Abreu</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Abreu</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1019,12 +1023,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Dalla Valle</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1037,12 +1041,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Ducru Beaucaillou</t>
+          <t>Trotanoy</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Ducru</t>
+          <t>Trotanoy</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1055,12 +1059,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Gaja</t>
+          <t>Ducru Beaucaillou</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>Gaja</t>
+          <t>Ducru</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1073,12 +1077,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Vieaux Chateau Certan</t>
+          <t>Gaja</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>VCC</t>
+          <t>Gaja</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1091,12 +1095,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Vieaux Chateau Certan</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>CarterCellars</t>
+          <t>VCC</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1109,12 +1113,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Petrus</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>PETRUS</t>
+          <t>CarterCellars</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1127,12 +1131,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Plumpjack</t>
+          <t>Petrus</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>PlumpJack</t>
+          <t>PETRUS</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1145,12 +1149,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Lokoya Winery</t>
+          <t>Plumpjack</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>ELEVATION</t>
+          <t>PlumpJack</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1163,52 +1167,52 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Combo - Barton + Poyferre</t>
+          <t>Lokoya Winery</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Leoville</t>
+          <t>ELEVATION</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Combo offer</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>Leoville Barton and Leoville Poyferre</t>
-        </is>
-      </c>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>La Mission Haut Brion</t>
+          <t>Combo - Barton + Poyferre</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>LaMission</t>
+          <t>Leoville</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="n"/>
+          <t>Combo offer</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Leoville Barton and Leoville Poyferre</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>La Mission Haut Brion</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>LaMission</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1221,12 +1225,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>d'Yquem</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Sauternes</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1239,12 +1243,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>La Conseillante</t>
+          <t>d'Yquem</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Conseillante</t>
+          <t>Sauternes</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1257,12 +1261,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Scarecrow - M. Etain</t>
+          <t>La Conseillante</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>TinMan</t>
+          <t>Conseillante</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1270,61 +1274,61 @@
           <t>Standalone Producer</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>M. Etain offer ONLY (excludes flagship Scarecrow bottles)</t>
-        </is>
-      </c>
+      <c r="D44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Combo - Araujo + Eisele</t>
+          <t>Scarecrow - M. Etain</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>Altagracia</t>
+          <t>TinMan</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Combo offer</t>
+          <t>Standalone Producer</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>Altagracia bottlings from Araujo / Eisele Vineyard</t>
+          <t>M. Etain offer ONLY (excludes flagship Scarecrow bottles)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Figeac</t>
+          <t>Combo - Araujo + Eisele</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>Figeac</t>
+          <t>Altagracia</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n"/>
+          <t>Combo offer</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>Altagracia bottlings from Araujo / Eisele Vineyard</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Pichon Baron</t>
+          <t>Figeac</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Baron</t>
+          <t>Figeac</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1337,12 +1341,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Bryant Family</t>
+          <t>Pichon Baron</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>BryantFam, DB4</t>
+          <t>Baron</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1350,21 +1354,17 @@
           <t>Standalone Producer</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>Include Bryant Bettina</t>
-        </is>
-      </c>
+      <c r="D48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Spottswoode</t>
+          <t>Bryant Family</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Spottswoode</t>
+          <t>BryantFam, DB4</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1372,57 +1372,61 @@
           <t>Standalone Producer</t>
         </is>
       </c>
-      <c r="D49" s="1" t="n"/>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>Include Bryant Bettina</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Other - California Whites</t>
+          <t>Spottswoode</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>SUMMER</t>
+          <t>Spottswoode</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Category offer</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>All California white wines</t>
-        </is>
-      </c>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Ulysses</t>
+          <t>Other - California Whites</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Ulysses</t>
+          <t>SUMMER</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="n"/>
+          <t>Category offer</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>All California white wines</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Ulysses</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Lafite</t>
+          <t>Ulysses</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1435,12 +1439,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Las Cases</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>LasCases</t>
+          <t>Lafite</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1453,12 +1457,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Cos d'Estournel</t>
+          <t>Las Cases</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>CosD</t>
+          <t>LasCases</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1471,12 +1475,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>William Fevre</t>
+          <t>Cos d'Estournel</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Fevre</t>
+          <t>CosD</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1489,12 +1493,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Canon</t>
+          <t>William Fevre</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Canon</t>
+          <t>Fevre</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1507,12 +1511,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Canon</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Canon</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1525,12 +1529,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Sine Qua Non</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>SQN10, SQN</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1543,12 +1547,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Caymus</t>
+          <t>Sine Qua Non</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Caymus</t>
+          <t>SQN10, SQN</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1561,12 +1565,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Roumier</t>
+          <t>Caymus</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>Roumier</t>
+          <t>Caymus</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1579,12 +1583,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Cardinale</t>
+          <t>Roumier</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Cardinale</t>
+          <t>Roumier</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1597,12 +1601,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Giacosa</t>
+          <t>Cardinale</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>Giacosa</t>
+          <t>Cardinale</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1615,12 +1619,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Dominus</t>
+          <t>Giacosa</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>Dominus</t>
+          <t>Giacosa</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1633,12 +1637,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Promontory</t>
+          <t>Dominus</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Promontory</t>
+          <t>Dominus</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1651,12 +1655,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Pichon Lalande</t>
+          <t>Promontory</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Lalande</t>
+          <t>Promontory</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -1669,12 +1673,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Fingers Crossed</t>
+          <t>Pichon Lalande</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Crossed</t>
+          <t>Lalande</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -1687,12 +1691,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Realm</t>
+          <t>Fingers Crossed</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>Realm</t>
+          <t>Crossed</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -1705,12 +1709,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>L'Evangile</t>
+          <t>Realm</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Evangile</t>
+          <t>Realm</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -1723,12 +1727,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Continuum</t>
+          <t>L'Evangile</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Continuum</t>
+          <t>Evangile</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -1741,12 +1745,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Vega Sicilia</t>
+          <t>Continuum</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Tempranillo</t>
+          <t>Continuum</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -1759,12 +1763,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Vega Sicilia</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Tempranillo</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -1777,12 +1781,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Poyferre</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Poyferre</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -1795,12 +1799,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Branaire Ducru</t>
+          <t>Poyferre</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Branaire</t>
+          <t>Poyferre</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -1813,12 +1817,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Peter Michael</t>
+          <t>Branaire Ducru</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>ThePoppies, PARADISE</t>
+          <t>Branaire</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -1831,12 +1835,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Futo</t>
+          <t>Peter Michael</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>FUTO</t>
+          <t>ThePoppies, PARADISE</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -1849,12 +1853,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Solaia</t>
+          <t>Futo</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>SOLAIA</t>
+          <t>FUTO</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -1867,12 +1871,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Joseph Phelps/Phelps Insignia</t>
+          <t>Solaia</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Phelps, INSIGNIA</t>
+          <t>SOLAIA</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -1885,52 +1889,52 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Other -Abandoned Cart</t>
+          <t>Joseph Phelps/Phelps Insignia</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>lastchance</t>
+          <t>Phelps, INSIGNIA</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Automation</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>Last Chance abandoned cart recovery email</t>
-        </is>
-      </c>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Clos Fourtet</t>
+          <t>Other -Abandoned Cart</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Fourtet</t>
+          <t>lastchance</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="n"/>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>Last Chance abandoned cart recovery email</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Comando G</t>
+          <t>Clos Fourtet</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>ComandoG</t>
+          <t>Fourtet</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -1943,12 +1947,12 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Lynch Bages</t>
+          <t>Comando G</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>LynchBages</t>
+          <t>ComandoG</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -1961,52 +1965,52 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>Combo - Peter Michael + Morlet</t>
+          <t>Lynch Bages</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>CAWhites</t>
+          <t>LynchBages</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>combo offer</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>White wines only</t>
-        </is>
-      </c>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Angelus</t>
+          <t>Combo - Peter Michael + Morlet</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Angelus</t>
+          <t>CAWhites</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="n"/>
+          <t>combo offer</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>White wines only</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>Chapoutier</t>
+          <t>Angelus</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>Chapoutier</t>
+          <t>Angelus</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2019,12 +2023,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>Batailley</t>
+          <t>Chapoutier</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Batailley</t>
+          <t>Chapoutier</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2037,12 +2041,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>Penfolds Grange</t>
+          <t>Batailley</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>Penfolds</t>
+          <t>Batailley</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -2055,12 +2059,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>Pontet Canet</t>
+          <t>Penfolds Grange</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>PontetCanet</t>
+          <t>Penfolds</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -2073,12 +2077,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>Eisele</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>EISELE</t>
+          <t>PontetCanet</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -2091,12 +2095,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>Calon Segur</t>
+          <t>Eisele</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>CalonSegur</t>
+          <t>EISELE</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -2109,12 +2113,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>Carruades de Lafite</t>
+          <t>Calon Segur</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>Carruades</t>
+          <t>CalonSegur</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -2127,12 +2131,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Scarecrow</t>
+          <t>Carruades de Lafite</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>Scarecrow</t>
+          <t>Carruades</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -2145,12 +2149,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>La Mondotte</t>
+          <t>Scarecrow</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Mondotte</t>
+          <t>Scarecrow</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -2163,12 +2167,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>Outpost</t>
+          <t>La Mondotte</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>OUTPOST</t>
+          <t>Mondotte</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -2181,12 +2185,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>Myriad</t>
+          <t>Outpost</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Beckstoffer</t>
+          <t>OUTPOST</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -2199,12 +2203,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>La Fleur Petrus</t>
+          <t>Myriad</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>Moueix</t>
+          <t>Beckstoffer</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -2217,12 +2221,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>Blankiet</t>
+          <t>La Fleur Petrus</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>Blankiet</t>
+          <t>Moueix</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -2235,12 +2239,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>L'Eglise Clinet</t>
+          <t>Blankiet</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>LegliseClinet</t>
+          <t>Blankiet</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -2253,12 +2257,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>Beringer</t>
+          <t>L'Eglise Clinet</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Beringer</t>
+          <t>LegliseClinet</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -2271,12 +2275,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>Masseto</t>
+          <t>Beringer</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Masseto</t>
+          <t>Beringer</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -2289,12 +2293,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>Rinaldi</t>
+          <t>Masseto</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Rinaldi</t>
+          <t>Masseto</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -2307,12 +2311,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>Clinet</t>
+          <t>Rinaldi</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Clinet</t>
+          <t>Rinaldi</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -2325,12 +2329,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>Fourrier</t>
+          <t>Clinet</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>Fourrier</t>
+          <t>Clinet</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -2343,52 +2347,52 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>Combo - Dom Perignon + Krug</t>
+          <t>Fourrier</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Bubbles</t>
+          <t>Fourrier</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Combo offer</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>champagne promotion including Dom Perignon and Krug</t>
-        </is>
-      </c>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>Malescot</t>
+          <t>Combo - Dom Perignon + Krug</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Malescot</t>
+          <t>Bubbles</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="n"/>
+          <t>Combo offer</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>champagne promotion including Dom Perignon and Krug</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>Troplong Mondot</t>
+          <t>Malescot</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Troplong</t>
+          <t>Malescot</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -2401,12 +2405,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>beychevelle</t>
+          <t>Troplong Mondot</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>Beychevelle</t>
+          <t>Troplong</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -2419,12 +2423,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>Tusk</t>
+          <t>beychevelle</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>Tusk</t>
+          <t>Beychevelle</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -2437,12 +2441,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>Dom Perignon</t>
+          <t>Tusk</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>DomP, DomPerignon</t>
+          <t>Tusk</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -2455,12 +2459,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>Staglin</t>
+          <t>Dom Perignon</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Staglin</t>
+          <t>DomP, DomPerignon</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -2473,12 +2477,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>La Gaffeliere</t>
+          <t>Staglin</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>Gaffeliere</t>
+          <t>Staglin</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -2491,12 +2495,12 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>Le Petit Cheval</t>
+          <t>La Gaffeliere</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>PetitCheval</t>
+          <t>Gaffeliere</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -2509,52 +2513,52 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>Combo - Cantenac Brown + Brane Cantenac</t>
+          <t>Le Petit Cheval</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>Cantenac</t>
+          <t>PetitCheval</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Combo offer</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>Cantenac Brown and Brane Cantenac</t>
-        </is>
-      </c>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>Pavie Macquin</t>
+          <t>Combo - Cantenac Brown + Brane Cantenac</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Macquin</t>
+          <t>Cantenac</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="n"/>
+          <t>Combo offer</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>Cantenac Brown and Brane Cantenac</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>Bellevue Mondotte</t>
+          <t>Pavie Macquin</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Bellevue</t>
+          <t>Macquin</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -2567,12 +2571,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>Bruno Clair</t>
+          <t>Bellevue Mondotte</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>BrunoClair</t>
+          <t>Bellevue</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -2585,12 +2589,12 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>Casanova di Neri</t>
+          <t>Bruno Clair</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Casanova</t>
+          <t>BrunoClair</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -2603,12 +2607,12 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>Saxum</t>
+          <t>Casanova di Neri</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Saxum</t>
+          <t>Casanova</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -2621,12 +2625,12 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Pape Clement</t>
+          <t>Saxum</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Graves</t>
+          <t>Saxum</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -2639,12 +2643,12 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Pape Clement</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Graves</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -2657,47 +2661,48 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
+          <t>Dunn</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>Dunn</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
           <t>Domaine Leflaive</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
+      <c r="B121" s="1" t="inlineStr">
         <is>
           <t>leflaive</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>seven stones</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>SevenStones</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cristal</t>
+          <t>seven stones</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>SevenStones</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2709,12 +2714,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Harlan Maiden</t>
+          <t>Cristal</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MAIDEN</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2726,12 +2731,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Poggio di Sotto</t>
+          <t>Harlan Maiden</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PoggioDiSotto</t>
+          <t>MAIDEN</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2743,12 +2748,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Marcassin</t>
+          <t>Poggio di Sotto</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Marcassin</t>
+          <t>PoggioDiSotto</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2760,12 +2765,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Chateau du Tertre</t>
+          <t>Marcassin</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TertreMargaux</t>
+          <t>Marcassin</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2777,12 +2782,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Chateau du Tertre</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lacoste</t>
+          <t>TertreMargaux</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2794,12 +2799,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Arnoux Vosnee Romanee</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Arnoux</t>
+          <t>Lacoste</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2811,12 +2816,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cerbaiona Brunello</t>
+          <t>Arnoux Vosnee Romanee</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cerbaiona</t>
+          <t>Arnoux</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2828,12 +2833,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Cerbaiona Brunello</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Cerbaiona</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2845,12 +2850,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Philip Togni</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Togni</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2862,12 +2867,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Philip Togni</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Pinault</t>
+          <t>Togni</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2879,12 +2884,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Bartolo Mascarello</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mascarello</t>
+          <t>Pinault</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2896,46 +2901,46 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>Bartolo Mascarello</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mascarello</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>Morlet</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Morlet</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="15" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Le Macchiole</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Messorio</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Kapscandy</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Kapcsandy</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2947,12 +2952,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>the Mascot</t>
+          <t>Kapscandy</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TheMascot</t>
+          <t>Kapcsandy</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2964,51 +2969,51 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pingus, Pingus Amelia</t>
+          <t>the Mascot</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>TheMascot</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
           <t>Standalone Producer</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Pingus Amelia is one product category from Pingus</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Pingus (including Pingus Amelia)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pingus</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Pingus Amelia is one product category from Pingus</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>Branaire Ducru</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Branaire</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Chateauneuf du Pape</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>CDP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3020,29 +3025,29 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
+          <t>Chateauneuf du Pape</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CDP</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>Gruaud Larose</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Gruaud</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Standalone Producer</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Rousseau chambertin mazis</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Rousseau</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3054,12 +3059,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>O'Shaughnessy</t>
+          <t>Rousseau chambertin mazis</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>O'Shaughnessy</t>
+          <t>Rousseau</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3071,32 +3076,304 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1982 Bordeaux</t>
+          <t>O'Shaughnessy</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BDX82</t>
+          <t>O'Shaughnessy</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>All Bordeaux in vintage 1982</t>
+          <t>Standalone Producer</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>1982 Bordeaux</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BDX82</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>All Bordeaux in vintage 1982</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Domaine Dujac</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Dujac</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Levy &amp; McClellan</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>LevyMcClellan</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Bonneau du Martray</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Bonneau</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Odette</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Odette</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Mugnier Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mugnier</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Montelena</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Montelena</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Verite</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Verite</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Bella Oaks</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BellaOaks</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Les Forts de Latour</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>LesForts</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Millot Echezeaux</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Millot</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Burlotto</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Burlotto</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Aubert</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Aubert</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Domaine Ponsot</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ponsot</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Dyquem</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sauteurnes</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>domaine jean grivot</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>grivot</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>Beausejour Duffau-Lagarrosse</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Duffau</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Standalone Producer</t>
         </is>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>SQN10, SQN</t>
+          <t>SQN10, SQN, ThirdTwin</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Kapcsandy</t>
+          <t>Kapscandy</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3365,17 +3365,92 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Beausejour Duffau-Lagarrosse</t>
+          <t>Haut-Brion Blanc</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Duffau</t>
+          <t>Blanc</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
           <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Smith Haut Lafitte</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HautLafitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jaboulet</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Hermitage</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Fontodi</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Fontodi</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Standalone Producer</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>chappellet</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>chappellet</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Cavallotto</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Cavallotto</t>
         </is>
       </c>
     </row>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3476,6 +3476,78 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Bevan Cellars</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Bevan</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Holiday Sale</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BigDaddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Pavie Decesse</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Perse</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Raya</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Raya</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Certan de May</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>DeMay</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Larcis Ducasse</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Larcis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3548,6 +3548,54 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Nine Suns</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>NineSuns</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Clos Erasmus</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Priorat</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Mersault White burgundy</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Meursault</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Rayas</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Rayas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -3475,6 +3475,11 @@
           <t>Cavallotto</t>
         </is>
       </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3487,6 +3492,11 @@
           <t>Bevan</t>
         </is>
       </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3511,6 +3521,11 @@
           <t>Perse</t>
         </is>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3523,6 +3538,11 @@
           <t>Raya</t>
         </is>
       </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3535,6 +3555,11 @@
           <t>DeMay</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3547,6 +3572,11 @@
           <t>Larcis</t>
         </is>
       </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3559,6 +3589,11 @@
           <t>NineSuns</t>
         </is>
       </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3571,6 +3606,11 @@
           <t>Priorat</t>
         </is>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3583,6 +3623,11 @@
           <t>Meursault</t>
         </is>
       </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3593,6 +3638,11 @@
       <c r="B177" t="inlineStr">
         <is>
           <t>Rayas</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
         </is>
       </c>
     </row>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Tempranillo</t>
+          <t>Unico, Tempranillo</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>ThePoppies, PARADISE</t>
+          <t>ThePoppies, PARADISE, Dancer</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="31.5703125" customWidth="1" min="1" max="1"/>
@@ -3646,6 +3646,23 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Le Dome</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>LeDome</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>standalone producer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Producer - Discount Code Mapping - Copy.xlsx
+++ b/Producer - Discount Code Mapping - Copy.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Morgan, WRAITH, HundredAcre</t>
+          <t>Morgan, WRAITH, HundredAcre, Fortunate</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
